--- a/KiCad/SEIENTS_EDD(Llista MOUSER).xlsx
+++ b/KiCad/SEIENTS_EDD(Llista MOUSER).xlsx
@@ -1,20 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="SpreadsheetGear 8.1.15.102"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakar\OneDrive\Documentos\PROJECTE_D_EDD\edd-project-grup-dijous-dj_d_seients\KiCad\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E503FE4-1B5C-441B-80BB-04A631BA8E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18075" windowHeight="9900"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="40001"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="351">
   <si>
     <t>Lead Time in Days</t>
   </si>
@@ -214,9 +225,6 @@
     <t>https://www.mouser.com/datasheet/3/507/7/phoenix_contact_1988587_en.pdf</t>
   </si>
   <si>
-    <t>Price 4 (EUR)</t>
-  </si>
-  <si>
     <t>KAF21BR71H104JM</t>
   </si>
   <si>
@@ -1064,100 +1072,22 @@
   </si>
   <si>
     <t>1.381</t>
+  </si>
+  <si>
+    <t>TOTAL DE COSTOS</t>
+  </si>
+  <si>
+    <t>Price by Order Unit (EUR)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="17">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1171,30 +1101,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri Light"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1220,18 +1127,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>23</xdr:col>
@@ -1247,7 +1170,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1289,7 +1218,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1331,7 +1266,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1373,7 +1314,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1415,7 +1362,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1457,7 +1410,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1499,7 +1458,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7"/>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1541,7 +1506,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8"/>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1583,7 +1554,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9"/>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1625,7 +1602,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10"/>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1667,7 +1650,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11"/>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1709,7 +1698,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12"/>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1751,7 +1746,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 13"/>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1793,7 +1794,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 14"/>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1835,7 +1842,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 15"/>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1877,7 +1890,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 16"/>
+        <xdr:cNvPr id="17" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1919,7 +1938,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 17"/>
+        <xdr:cNvPr id="18" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -1961,7 +1986,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 18"/>
+        <xdr:cNvPr id="19" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2003,7 +2034,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Picture 19"/>
+        <xdr:cNvPr id="20" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2045,7 +2082,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Picture 20"/>
+        <xdr:cNvPr id="21" name="Picture 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2087,7 +2130,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Picture 21"/>
+        <xdr:cNvPr id="22" name="Picture 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2129,7 +2178,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Picture 22"/>
+        <xdr:cNvPr id="23" name="Picture 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2171,7 +2226,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Picture 23"/>
+        <xdr:cNvPr id="24" name="Picture 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2213,7 +2274,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Picture 24"/>
+        <xdr:cNvPr id="25" name="Picture 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2255,7 +2322,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Picture 25"/>
+        <xdr:cNvPr id="26" name="Picture 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2297,7 +2370,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Picture 26"/>
+        <xdr:cNvPr id="27" name="Picture 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2339,7 +2418,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Picture 27"/>
+        <xdr:cNvPr id="28" name="Picture 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2381,7 +2466,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="Picture 28"/>
+        <xdr:cNvPr id="29" name="Picture 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2423,7 +2514,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="Picture 29"/>
+        <xdr:cNvPr id="30" name="Picture 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2465,7 +2562,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="Picture 30"/>
+        <xdr:cNvPr id="31" name="Picture 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2507,7 +2610,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="Picture 31"/>
+        <xdr:cNvPr id="32" name="Picture 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2549,7 +2658,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="Picture 32"/>
+        <xdr:cNvPr id="33" name="Picture 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2591,7 +2706,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Picture 33"/>
+        <xdr:cNvPr id="34" name="Picture 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2633,7 +2754,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Picture 34"/>
+        <xdr:cNvPr id="35" name="Picture 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2675,7 +2802,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Picture 35"/>
+        <xdr:cNvPr id="36" name="Picture 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2717,7 +2850,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Picture 36"/>
+        <xdr:cNvPr id="37" name="Picture 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2759,7 +2898,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Picture 37"/>
+        <xdr:cNvPr id="38" name="Picture 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2801,7 +2946,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="Picture 38"/>
+        <xdr:cNvPr id="39" name="Picture 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -3119,2470 +3270,2642 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y39"/>
-  <sheetFormatPr defaultRowHeight="14.95"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.90234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.03125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.40234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="135.640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.21484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.35546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1484375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.91796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.35546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.76171875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.40625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.96875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.66015625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.234375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.046875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.859375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="135.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="182.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.6796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="46.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="46.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row>
-      <c s="1" t="s">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>176</v>
       </c>
-      <c s="1" t="s">
-        <v>46</v>
-      </c>
-      <c s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K2">
+        <f>I2*J2</f>
+        <v>1.6379999999999999</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>104</v>
       </c>
-      <c s="1" t="s">
-        <v>177</v>
-      </c>
-      <c s="1" t="s">
-        <v>225</v>
-      </c>
-      <c s="1" t="s">
-        <v>199</v>
-      </c>
-      <c s="1" t="s">
-        <v>326</v>
-      </c>
-      <c s="1" t="s">
-        <v>200</v>
-      </c>
-      <c s="1" t="s">
-        <v>226</v>
-      </c>
-      <c s="1" t="s">
-        <v>134</v>
-      </c>
-      <c s="1" t="s">
-        <v>66</v>
-      </c>
-      <c s="1" t="s">
-        <v>261</v>
-      </c>
-      <c s="1" t="s">
-        <v>156</v>
-      </c>
-      <c s="1" t="s">
-        <v>157</v>
-      </c>
-      <c s="1" t="s">
-        <v>0</v>
-      </c>
-      <c s="1" t="s">
-        <v>201</v>
-      </c>
-      <c s="1" t="s">
-        <v>158</v>
-      </c>
-      <c s="1" t="s">
-        <v>82</v>
-      </c>
-      <c s="1" t="s">
-        <v>262</v>
-      </c>
-      <c s="1" t="s">
-        <v>47</v>
-      </c>
-      <c s="1" t="s">
-        <v>83</v>
-      </c>
-      <c s="1" t="s">
+      <c r="T2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>227</v>
       </c>
-      <c s="1" t="s">
-        <v>1</v>
-      </c>
-      <c s="1" t="s">
-        <v>135</v>
-      </c>
-      <c s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>67</v>
       </c>
-      <c s="1" t="s">
-        <v>67</v>
-      </c>
-      <c s="1" t="s">
-        <v>327</v>
-      </c>
-      <c s="1" t="s">
-        <v>84</v>
-      </c>
-      <c s="1" t="s">
-        <v>178</v>
-      </c>
-      <c s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>48</v>
-      </c>
-      <c s="1" t="s">
-        <v>25</v>
-      </c>
-      <c s="1" t="s">
-        <v>87</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>68</v>
-      </c>
-      <c s="1" t="s">
-        <v>329</v>
       </c>
       <c r="Y2" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>330</v>
-      </c>
-      <c s="1" t="s">
-        <v>330</v>
-      </c>
-      <c s="1" t="s">
+    <row r="3" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>49</v>
       </c>
-      <c s="1" t="s">
-        <v>84</v>
-      </c>
-      <c s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K39" si="0">I3*J3</f>
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>159</v>
       </c>
-      <c s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
+    </row>
+    <row r="4" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>264</v>
       </c>
-      <c s="1" t="s">
-        <v>25</v>
-      </c>
-      <c s="1" t="s">
-        <v>87</v>
-      </c>
-      <c s="1" t="s">
-        <v>229</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>27</v>
-      </c>
-      <c s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>5</v>
-      </c>
-      <c s="1" t="s">
-        <v>5</v>
-      </c>
-      <c s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>245</v>
       </c>
-      <c s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>1.548</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>69</v>
-      </c>
-      <c s="1" t="s">
-        <v>265</v>
-      </c>
-      <c s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>247</v>
-      </c>
-      <c s="1" t="s">
-        <v>202</v>
-      </c>
-      <c s="1" t="s">
-        <v>203</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>204</v>
-      </c>
-      <c s="1" t="s">
-        <v>70</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>309</v>
-      </c>
-      <c s="1" t="s">
-        <v>309</v>
-      </c>
-      <c s="1" t="s">
+    <row r="5" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c s="1" t="s">
-        <v>84</v>
-      </c>
-      <c s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>106</v>
       </c>
-      <c s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="M5" s="1" t="s">
+      <c r="O5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>86</v>
       </c>
-      <c s="1" t="s">
-        <v>107</v>
-      </c>
-      <c s="1" t="s">
-        <v>25</v>
-      </c>
-      <c s="1" t="s">
+      <c r="Q5" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="1" t="s">
         <v>87</v>
       </c>
-      <c s="1" t="s">
-        <v>180</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>27</v>
-      </c>
-      <c s="1" t="s">
+      <c r="Y5" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="Y5" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>7</v>
-      </c>
-      <c s="1" t="s">
-        <v>7</v>
-      </c>
-      <c s="1" t="s">
+      <c r="I6" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W6" s="1" t="s">
         <v>205</v>
-      </c>
-      <c s="1" t="s">
-        <v>71</v>
-      </c>
-      <c s="1" t="s">
-        <v>136</v>
-      </c>
-      <c s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>231</v>
-      </c>
-      <c s="1" t="s">
-        <v>284</v>
-      </c>
-      <c s="1" t="s">
-        <v>28</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>50</v>
-      </c>
-      <c s="1" t="s">
-        <v>206</v>
       </c>
       <c r="Y6" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>266</v>
-      </c>
-      <c s="1" t="s">
-        <v>266</v>
-      </c>
-      <c s="1" t="s">
+    <row r="7" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c s="1" t="s">
-        <v>71</v>
-      </c>
-      <c s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>51</v>
       </c>
-      <c s="1" t="s">
-        <v>248</v>
+      <c r="F7" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>248</v>
+        <v>229</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>0.52500000000000002</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>285</v>
-      </c>
-      <c s="1" t="s">
-        <v>108</v>
-      </c>
-      <c s="1" t="s">
-        <v>162</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q7" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>331</v>
-      </c>
-      <c s="1" t="s">
-        <v>181</v>
+      <c r="R7" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="Y7" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>249</v>
-      </c>
-      <c s="1" t="s">
-        <v>249</v>
-      </c>
-      <c s="1" t="s">
-        <v>182</v>
-      </c>
-      <c s="1" t="s">
+    <row r="8" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
-      <c s="1" t="s">
+      <c r="E8" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>286</v>
       </c>
-      <c s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>109</v>
-      </c>
-      <c s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="W9" s="1" t="s">
         <v>207</v>
-      </c>
-      <c s="1" t="s">
-        <v>163</v>
-      </c>
-      <c s="1" t="s">
-        <v>180</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>8</v>
-      </c>
-      <c s="1" t="s">
-        <v>332</v>
-      </c>
-      <c s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>287</v>
-      </c>
-      <c s="1" t="s">
-        <v>287</v>
-      </c>
-      <c s="1" t="s">
-        <v>52</v>
-      </c>
-      <c s="1" t="s">
-        <v>71</v>
-      </c>
-      <c s="1" t="s">
-        <v>31</v>
-      </c>
-      <c s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>53</v>
-      </c>
-      <c s="1" t="s">
-        <v>108</v>
-      </c>
-      <c s="1" t="s">
-        <v>162</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>288</v>
-      </c>
-      <c s="1" t="s">
-        <v>208</v>
       </c>
       <c r="Y9" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>310</v>
-      </c>
-      <c s="1" t="s">
-        <v>310</v>
-      </c>
-      <c s="1" t="s">
+    <row r="10" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>91</v>
       </c>
-      <c s="1" t="s">
-        <v>92</v>
-      </c>
-      <c s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>32</v>
       </c>
-      <c s="1" t="s">
-        <v>333</v>
+      <c r="F10" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>333</v>
+        <v>229</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>0.56799999999999995</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>111</v>
-      </c>
-      <c s="1" t="s">
-        <v>289</v>
-      </c>
-      <c s="1" t="s">
-        <v>268</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q10" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
+      <c r="R10" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V10" s="1" t="s">
         <v>54</v>
       </c>
-      <c s="1" t="s">
-        <v>183</v>
+      <c r="W10" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="11" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c s="1" t="s">
-        <v>250</v>
-      </c>
-      <c s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>55</v>
       </c>
-      <c s="1" t="s">
+      <c r="E11" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>5.74</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="W11" s="1" t="s">
         <v>311</v>
-      </c>
-      <c s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>334</v>
-      </c>
-      <c s="1" t="s">
-        <v>112</v>
-      </c>
-      <c s="1" t="s">
-        <v>72</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>113</v>
-      </c>
-      <c s="1" t="s">
-        <v>114</v>
-      </c>
-      <c s="1" t="s">
-        <v>312</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>232</v>
-      </c>
-      <c s="1" t="s">
+    <row r="12" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>9.15</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="V12" s="1" t="s">
         <v>269</v>
       </c>
-      <c s="1" t="s">
-        <v>209</v>
-      </c>
-      <c s="1" t="s">
-        <v>115</v>
-      </c>
-      <c s="1" t="s">
-        <v>210</v>
-      </c>
-      <c s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>34</v>
-      </c>
-      <c s="1" t="s">
-        <v>117</v>
-      </c>
-      <c s="1" t="s">
-        <v>268</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>164</v>
-      </c>
-      <c s="1" t="s">
-        <v>270</v>
-      </c>
-      <c s="1" t="s">
-        <v>335</v>
+      <c r="W12" s="1" t="s">
+        <v>334</v>
       </c>
       <c r="Y12" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>93</v>
-      </c>
-      <c s="1" t="s">
-        <v>93</v>
-      </c>
-      <c s="1" t="s">
-        <v>313</v>
-      </c>
-      <c s="1" t="s">
-        <v>290</v>
-      </c>
-      <c s="1" t="s">
-        <v>184</v>
-      </c>
-      <c s="1" t="s">
+    <row r="13" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>2.35</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="M13" s="1" t="s">
+      <c r="O13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>86</v>
       </c>
-      <c s="1" t="s">
-        <v>138</v>
-      </c>
-      <c s="1" t="s">
-        <v>25</v>
-      </c>
-      <c s="1" t="s">
-        <v>87</v>
-      </c>
-      <c s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>204</v>
-      </c>
-      <c s="1" t="s">
-        <v>211</v>
+      <c r="R13" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="Y13" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="14" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>0.86</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W14" s="1" t="s">
         <v>291</v>
       </c>
-      <c s="1" t="s">
-        <v>139</v>
-      </c>
-      <c s="1" t="s">
-        <v>314</v>
-      </c>
-      <c s="1" t="s">
+      <c r="Y14" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>55</v>
       </c>
-      <c s="1" t="s">
-        <v>140</v>
-      </c>
-      <c s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
+      <c r="E15" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>1.04</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="W15" s="1" t="s">
         <v>212</v>
-      </c>
-      <c s="1" t="s">
-        <v>207</v>
-      </c>
-      <c s="1" t="s">
-        <v>163</v>
-      </c>
-      <c s="1" t="s">
-        <v>180</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>113</v>
-      </c>
-      <c s="1" t="s">
-        <v>35</v>
-      </c>
-      <c s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>316</v>
-      </c>
-      <c s="1" t="s">
-        <v>56</v>
-      </c>
-      <c s="1" t="s">
-        <v>36</v>
-      </c>
-      <c s="1" t="s">
-        <v>55</v>
-      </c>
-      <c s="1" t="s">
-        <v>118</v>
-      </c>
-      <c s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>119</v>
-      </c>
-      <c s="1" t="s">
-        <v>108</v>
-      </c>
-      <c s="1" t="s">
-        <v>162</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>164</v>
-      </c>
-      <c s="1" t="s">
-        <v>271</v>
-      </c>
-      <c s="1" t="s">
-        <v>213</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="16" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>165</v>
       </c>
-      <c s="1" t="s">
+      <c r="I16" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>165</v>
       </c>
-      <c s="1" t="s">
-        <v>37</v>
-      </c>
-      <c s="1" t="s">
-        <v>185</v>
-      </c>
-      <c s="1" t="s">
-        <v>336</v>
-      </c>
-      <c s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>166</v>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>1.57</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>120</v>
-      </c>
-      <c s="1" t="s">
-        <v>214</v>
-      </c>
-      <c s="1" t="s">
-        <v>95</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q16" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
+      <c r="R16" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V16" s="1" t="s">
         <v>27</v>
       </c>
-      <c s="1" t="s">
-        <v>317</v>
+      <c r="W16" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="Y16" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="17" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>293</v>
       </c>
-      <c s="1" t="s">
-        <v>293</v>
-      </c>
-      <c s="1" t="s">
-        <v>294</v>
-      </c>
-      <c s="1" t="s">
-        <v>290</v>
-      </c>
-      <c s="1" t="s">
-        <v>337</v>
-      </c>
-      <c s="1" t="s">
-        <v>272</v>
+      <c r="D17" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>272</v>
+        <v>229</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>1.01</v>
       </c>
       <c r="M17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" s="1" t="s">
         <v>86</v>
       </c>
-      <c s="1" t="s">
+      <c r="Q17" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>25</v>
-      </c>
-      <c s="1" t="s">
-        <v>87</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>318</v>
-      </c>
-      <c s="1" t="s">
+      <c r="R17" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="W17" s="1" t="s">
         <v>57</v>
       </c>
       <c r="Y17" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>96</v>
-      </c>
-      <c s="1" t="s">
-        <v>96</v>
-      </c>
-      <c s="1" t="s">
-        <v>73</v>
-      </c>
-      <c s="1" t="s">
+    <row r="18" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>55</v>
       </c>
-      <c s="1" t="s">
-        <v>141</v>
-      </c>
-      <c s="1" t="s">
-        <v>94</v>
+      <c r="E18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>94</v>
+        <v>229</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>1.04</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N18" s="1" t="s">
         <v>10</v>
       </c>
-      <c s="1" t="s">
-        <v>186</v>
-      </c>
-      <c s="1" t="s">
+      <c r="O18" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U18" s="1" t="s">
         <v>163</v>
       </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>164</v>
-      </c>
-      <c s="1" t="s">
-        <v>271</v>
-      </c>
-      <c s="1" t="s">
-        <v>319</v>
+      <c r="V18" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>318</v>
       </c>
       <c r="Y18" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="19" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>187</v>
       </c>
-      <c s="1" t="s">
+      <c r="I19" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>187</v>
       </c>
-      <c s="1" t="s">
-        <v>74</v>
-      </c>
-      <c s="1" t="s">
-        <v>290</v>
-      </c>
-      <c s="1" t="s">
-        <v>273</v>
-      </c>
-      <c s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>188</v>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>1.47</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>167</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="P19" s="1" t="s">
         <v>295</v>
       </c>
-      <c s="1" t="s">
-        <v>296</v>
-      </c>
-      <c s="1" t="s">
+      <c r="Q19" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>164</v>
-      </c>
-      <c s="1" t="s">
-        <v>215</v>
-      </c>
-      <c s="1" t="s">
+      <c r="R19" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="W19" s="1" t="s">
         <v>11</v>
       </c>
       <c r="Y19" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="20" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>5.99</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="W20" s="1" t="s">
         <v>297</v>
-      </c>
-      <c s="1" t="s">
-        <v>297</v>
-      </c>
-      <c s="1" t="s">
-        <v>320</v>
-      </c>
-      <c s="1" t="s">
-        <v>290</v>
-      </c>
-      <c s="1" t="s">
-        <v>12</v>
-      </c>
-      <c s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>58</v>
-      </c>
-      <c s="1" t="s">
-        <v>25</v>
-      </c>
-      <c s="1" t="s">
-        <v>87</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>164</v>
-      </c>
-      <c s="1" t="s">
-        <v>121</v>
-      </c>
-      <c s="1" t="s">
-        <v>298</v>
       </c>
       <c r="Y20" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="21" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>13</v>
       </c>
-      <c s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>13</v>
       </c>
-      <c s="1" t="s">
-        <v>338</v>
-      </c>
-      <c s="1" t="s">
-        <v>233</v>
-      </c>
-      <c s="1" t="s">
-        <v>189</v>
-      </c>
-      <c s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="K21">
+        <f t="shared" si="0"/>
+        <v>3.6320000000000001</v>
+      </c>
       <c r="M21" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="O21" s="1" t="s">
         <v>299</v>
       </c>
-      <c s="1" t="s">
-        <v>300</v>
-      </c>
-      <c s="1" t="s">
+      <c r="P21" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="W21" s="1" t="s">
         <v>274</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>288</v>
-      </c>
-      <c s="1" t="s">
-        <v>275</v>
       </c>
       <c r="Y21" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>142</v>
-      </c>
-      <c s="1" t="s">
-        <v>142</v>
-      </c>
-      <c s="1" t="s">
-        <v>169</v>
-      </c>
-      <c s="1" t="s">
-        <v>339</v>
-      </c>
-      <c s="1" t="s">
+    <row r="22" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="0"/>
+        <v>0.74</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>251</v>
       </c>
-      <c s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="M22" s="1" t="s">
+      <c r="O22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>86</v>
       </c>
-      <c s="1" t="s">
+      <c r="Q22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="W22" s="1" t="s">
         <v>252</v>
-      </c>
-      <c s="1" t="s">
-        <v>25</v>
-      </c>
-      <c s="1" t="s">
-        <v>87</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>288</v>
-      </c>
-      <c s="1" t="s">
-        <v>253</v>
       </c>
       <c r="Y22" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="23" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="0"/>
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="P23" s="1" t="s">
         <v>277</v>
       </c>
-      <c s="1" t="s">
-        <v>277</v>
-      </c>
-      <c s="1" t="s">
-        <v>143</v>
-      </c>
-      <c s="1" t="s">
-        <v>60</v>
-      </c>
-      <c s="1" t="s">
-        <v>14</v>
-      </c>
-      <c s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>190</v>
-      </c>
-      <c s="1" t="s">
-        <v>321</v>
-      </c>
-      <c s="1" t="s">
-        <v>278</v>
-      </c>
-      <c s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>288</v>
-      </c>
-      <c s="1" t="s">
-        <v>254</v>
+      <c r="R23" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="Y23" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="24" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="0"/>
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="W24" s="1" t="s">
         <v>170</v>
-      </c>
-      <c s="1" t="s">
-        <v>170</v>
-      </c>
-      <c s="1" t="s">
-        <v>279</v>
-      </c>
-      <c s="1" t="s">
-        <v>39</v>
-      </c>
-      <c s="1" t="s">
-        <v>340</v>
-      </c>
-      <c s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>76</v>
-      </c>
-      <c s="1" t="s">
-        <v>295</v>
-      </c>
-      <c s="1" t="s">
-        <v>296</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>288</v>
-      </c>
-      <c s="1" t="s">
-        <v>171</v>
       </c>
       <c r="Y24" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>216</v>
-      </c>
-      <c s="1" t="s">
-        <v>216</v>
-      </c>
-      <c s="1" t="s">
-        <v>122</v>
-      </c>
-      <c s="1" t="s">
-        <v>339</v>
-      </c>
-      <c s="1" t="s">
-        <v>322</v>
-      </c>
-      <c s="1" t="s">
-        <v>255</v>
+    <row r="25" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>61</v>
       </c>
+      <c r="K25">
+        <f t="shared" si="0"/>
+        <v>1.1520000000000001</v>
+      </c>
       <c r="M25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P25" s="1" t="s">
         <v>86</v>
       </c>
-      <c s="1" t="s">
-        <v>172</v>
-      </c>
-      <c s="1" t="s">
-        <v>25</v>
-      </c>
-      <c s="1" t="s">
-        <v>87</v>
-      </c>
-      <c s="1" t="s">
+      <c r="Q25" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>288</v>
-      </c>
-      <c s="1" t="s">
-        <v>253</v>
+      <c r="R25" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="Y25" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="26" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>62</v>
       </c>
-      <c s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>62</v>
       </c>
-      <c s="1" t="s">
-        <v>217</v>
-      </c>
-      <c s="1" t="s">
-        <v>280</v>
-      </c>
-      <c s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>234</v>
       </c>
-      <c s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="I26" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>235</v>
+        <v>229</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="0"/>
+        <v>0.189</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>123</v>
       </c>
-      <c s="1" t="s">
-        <v>124</v>
-      </c>
-      <c s="1" t="s">
-        <v>256</v>
-      </c>
-      <c s="1" t="s">
+      <c r="P26" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q26" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>228</v>
-      </c>
-      <c s="1" t="s">
-        <v>288</v>
-      </c>
-      <c s="1" t="s">
-        <v>144</v>
+      <c r="R26" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="Y26" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="27" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="0"/>
+        <v>1.52</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="O27" s="1" t="s">
         <v>125</v>
       </c>
-      <c s="1" t="s">
-        <v>125</v>
-      </c>
-      <c s="1" t="s">
-        <v>145</v>
-      </c>
-      <c s="1" t="s">
-        <v>301</v>
-      </c>
-      <c s="1" t="s">
-        <v>146</v>
-      </c>
-      <c s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>147</v>
-      </c>
-      <c s="1" t="s">
-        <v>126</v>
-      </c>
-      <c s="1" t="s">
+      <c r="P27" s="1" t="s">
         <v>15</v>
       </c>
-      <c s="1" t="s">
+      <c r="Q27" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>164</v>
-      </c>
-      <c s="1" t="s">
+      <c r="R27" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="V27" s="1" t="s">
         <v>54</v>
       </c>
-      <c s="1" t="s">
+      <c r="W27" s="1" t="s">
         <v>16</v>
       </c>
       <c r="Y27" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="28" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>191</v>
       </c>
-      <c s="1" t="s">
-        <v>191</v>
-      </c>
-      <c s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>127</v>
       </c>
-      <c s="1" t="s">
-        <v>60</v>
-      </c>
-      <c s="1" t="s">
-        <v>192</v>
-      </c>
-      <c s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="I28" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>128</v>
+        <v>229</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="0"/>
+        <v>4.68</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>218</v>
-      </c>
-      <c s="1" t="s">
-        <v>321</v>
-      </c>
-      <c s="1" t="s">
-        <v>278</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q28" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>302</v>
-      </c>
-      <c s="1" t="s">
-        <v>97</v>
-      </c>
-      <c s="1" t="s">
-        <v>236</v>
+      <c r="R28" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="Y28" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>237</v>
-      </c>
-      <c s="1" t="s">
-        <v>237</v>
-      </c>
-      <c s="1" t="s">
-        <v>342</v>
-      </c>
-      <c s="1" t="s">
-        <v>77</v>
-      </c>
-      <c s="1" t="s">
+    <row r="29" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="0"/>
+        <v>1.04</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="O29" s="1" t="s">
         <v>148</v>
       </c>
-      <c s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>98</v>
-      </c>
-      <c s="1" t="s">
-        <v>149</v>
-      </c>
-      <c s="1" t="s">
-        <v>186</v>
-      </c>
-      <c s="1" t="s">
+      <c r="P29" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q29" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>302</v>
-      </c>
-      <c s="1" t="s">
-        <v>318</v>
-      </c>
-      <c s="1" t="s">
-        <v>129</v>
+      <c r="R29" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="Y29" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="30" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>173</v>
       </c>
-      <c s="1" t="s">
-        <v>173</v>
-      </c>
-      <c s="1" t="s">
-        <v>17</v>
-      </c>
-      <c s="1" t="s">
-        <v>174</v>
-      </c>
-      <c s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>18</v>
       </c>
-      <c s="1" t="s">
-        <v>323</v>
+      <c r="F30" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c s="1" t="s">
-        <v>323</v>
+        <v>307</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="0"/>
+        <v>0.65400000000000003</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>99</v>
-      </c>
-      <c s="1" t="s">
-        <v>149</v>
-      </c>
-      <c s="1" t="s">
-        <v>186</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q30" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>302</v>
-      </c>
-      <c s="1" t="s">
-        <v>281</v>
-      </c>
-      <c s="1" t="s">
-        <v>219</v>
+      <c r="R30" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="Y30" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>130</v>
-      </c>
-      <c s="1" t="s">
-        <v>130</v>
-      </c>
-      <c s="1" t="s">
-        <v>78</v>
-      </c>
-      <c s="1" t="s">
-        <v>343</v>
-      </c>
-      <c s="1" t="s">
-        <v>257</v>
-      </c>
-      <c s="1" t="s">
-        <v>238</v>
+    <row r="31" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>238</v>
+        <v>229</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="0"/>
+        <v>0.20599999999999999</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>220</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>19</v>
       </c>
-      <c s="1" t="s">
+      <c r="P31" s="1" t="s">
         <v>20</v>
       </c>
-      <c s="1" t="s">
+      <c r="Q31" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>302</v>
-      </c>
-      <c s="1" t="s">
-        <v>288</v>
-      </c>
-      <c s="1" t="s">
+      <c r="R31" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="W31" s="1" t="s">
         <v>21</v>
       </c>
       <c r="Y31" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>344</v>
-      </c>
-      <c s="1" t="s">
-        <v>344</v>
-      </c>
-      <c s="1" t="s">
-        <v>131</v>
-      </c>
-      <c s="1" t="s">
-        <v>174</v>
-      </c>
-      <c s="1" t="s">
-        <v>239</v>
-      </c>
-      <c s="1" t="s">
+    <row r="32" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="K32">
+        <f t="shared" si="0"/>
+        <v>0.39600000000000002</v>
+      </c>
       <c r="M32" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N32" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>149</v>
-      </c>
-      <c s="1" t="s">
-        <v>186</v>
-      </c>
-      <c s="1" t="s">
+      <c r="O32" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q32" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>302</v>
-      </c>
-      <c s="1" t="s">
-        <v>281</v>
-      </c>
-      <c s="1" t="s">
-        <v>219</v>
+      <c r="R32" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="Y32" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>303</v>
-      </c>
-      <c s="1" t="s">
-        <v>303</v>
-      </c>
-      <c s="1" t="s">
+    <row r="33" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="0"/>
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W33" s="1" t="s">
         <v>193</v>
-      </c>
-      <c s="1" t="s">
-        <v>240</v>
-      </c>
-      <c s="1" t="s">
-        <v>100</v>
-      </c>
-      <c s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>63</v>
-      </c>
-      <c s="1" t="s">
-        <v>241</v>
-      </c>
-      <c s="1" t="s">
-        <v>278</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>54</v>
-      </c>
-      <c s="1" t="s">
-        <v>194</v>
       </c>
       <c r="Y33" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>195</v>
-      </c>
-      <c s="1" t="s">
-        <v>195</v>
-      </c>
-      <c s="1" t="s">
+    <row r="34" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="0"/>
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="V34" s="1" t="s">
         <v>221</v>
       </c>
-      <c s="1" t="s">
-        <v>101</v>
-      </c>
-      <c s="1" t="s">
-        <v>242</v>
-      </c>
-      <c s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>22</v>
-      </c>
-      <c s="1" t="s">
-        <v>23</v>
-      </c>
-      <c s="1" t="s">
-        <v>102</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>302</v>
-      </c>
-      <c s="1" t="s">
-        <v>222</v>
-      </c>
-      <c s="1" t="s">
-        <v>132</v>
+      <c r="W34" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="Y34" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>324</v>
-      </c>
-      <c s="1" t="s">
-        <v>324</v>
-      </c>
-      <c s="1" t="s">
+    <row r="35" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>151</v>
       </c>
-      <c s="1" t="s">
+      <c r="E35" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>152</v>
       </c>
-      <c s="1" t="s">
-        <v>175</v>
-      </c>
-      <c s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="I35" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>153</v>
+        <v>229</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="0"/>
+        <v>2.39</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P35" s="1" t="s">
         <v>196</v>
       </c>
-      <c s="1" t="s">
-        <v>41</v>
-      </c>
-      <c s="1" t="s">
-        <v>197</v>
-      </c>
-      <c s="1" t="s">
+      <c r="Q35" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
+      <c r="R35" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U35" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
+      <c r="V35" s="1" t="s">
         <v>42</v>
       </c>
-      <c s="1" t="s">
-        <v>258</v>
+      <c r="W35" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="Y35" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>304</v>
-      </c>
-      <c s="1" t="s">
-        <v>304</v>
-      </c>
-      <c s="1" t="s">
-        <v>154</v>
-      </c>
-      <c s="1" t="s">
-        <v>152</v>
-      </c>
-      <c s="1" t="s">
-        <v>325</v>
-      </c>
-      <c s="1" t="s">
-        <v>79</v>
+    <row r="36" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>79</v>
+        <v>229</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="0"/>
+        <v>1.1200000000000001</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>346</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>19</v>
       </c>
-      <c s="1" t="s">
+      <c r="P36" s="1" t="s">
         <v>20</v>
       </c>
-      <c s="1" t="s">
+      <c r="Q36" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
+      <c r="R36" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U36" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
+      <c r="V36" s="1" t="s">
         <v>42</v>
       </c>
-      <c s="1" t="s">
+      <c r="W36" s="1" t="s">
         <v>64</v>
       </c>
       <c r="Y36" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
-        <v>103</v>
-      </c>
-      <c s="1" t="s">
-        <v>103</v>
-      </c>
-      <c s="1" t="s">
+    <row r="37" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>223</v>
       </c>
-      <c s="1" t="s">
-        <v>224</v>
-      </c>
-      <c s="1" t="s">
-        <v>243</v>
-      </c>
-      <c s="1" t="s">
-        <v>347</v>
+      <c r="E37" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>346</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>347</v>
+        <v>229</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="0"/>
+        <v>2.2599999999999998</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>80</v>
-      </c>
-      <c s="1" t="s">
-        <v>117</v>
-      </c>
-      <c s="1" t="s">
-        <v>268</v>
-      </c>
-      <c s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q37" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>113</v>
-      </c>
-      <c s="1" t="s">
+      <c r="R37" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="V37" s="1" t="s">
         <v>24</v>
       </c>
-      <c s="1" t="s">
-        <v>259</v>
+      <c r="W37" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="Y37" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="38" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>43</v>
       </c>
-      <c s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>43</v>
       </c>
-      <c s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>44</v>
       </c>
-      <c s="1" t="s">
-        <v>260</v>
-      </c>
-      <c s="1" t="s">
-        <v>198</v>
-      </c>
-      <c s="1" t="s">
+      <c r="D38" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="0"/>
+        <v>2.91</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N38" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>349</v>
-      </c>
-      <c s="1" t="s">
-        <v>117</v>
-      </c>
-      <c s="1" t="s">
-        <v>268</v>
-      </c>
-      <c s="1" t="s">
+      <c r="O38" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q38" s="1" t="s">
         <v>3</v>
       </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>113</v>
-      </c>
-      <c s="1" t="s">
+      <c r="R38" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="V38" s="1" t="s">
         <v>45</v>
       </c>
-      <c s="1" t="s">
-        <v>244</v>
+      <c r="W38" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="Y38" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row ht="60" customHeight="1">
-      <c s="1" t="s">
+    <row r="39" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>305</v>
       </c>
-      <c s="1" t="s">
+      <c r="I39" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>305</v>
       </c>
-      <c s="1" t="s">
-        <v>155</v>
-      </c>
-      <c s="1" t="s">
-        <v>152</v>
-      </c>
-      <c s="1" t="s">
-        <v>133</v>
-      </c>
-      <c s="1" t="s">
+      <c r="K39">
+        <f t="shared" si="0"/>
+        <v>2.7600000000000002</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N39" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c s="1" t="s">
-        <v>307</v>
-      </c>
-      <c s="1" t="s">
+      <c r="O39" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="V39" s="1" t="s">
         <v>282</v>
       </c>
-      <c s="1" t="s">
-        <v>72</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>105</v>
-      </c>
-      <c s="1" t="s">
-        <v>328</v>
-      </c>
-      <c s="1" t="s">
-        <v>3</v>
-      </c>
-      <c s="1" t="s">
-        <v>283</v>
-      </c>
-      <c s="1" t="s">
+      <c r="W39" s="1" t="s">
         <v>65</v>
       </c>
       <c r="Y39" s="1" t="s">
         <v>59</v>
       </c>
     </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="C40" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40">
+        <f>SUM(K2:K39)</f>
+        <v>63.863000000000007</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C40:J40"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>